--- a/week-01/Ex5B_FinalResults.xlsx
+++ b/week-01/Ex5B_FinalResults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caglacelik/Documents/DataAnalytics/week-01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725BE0B0-7E80-C341-A548-241336A49547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27228B2D-AF3D-384C-AB51-C1224F9F6DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="440" yWindow="760" windowWidth="28800" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="33" r:id="rId3"/>
+    <pivotCache cacheId="11" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -341,8 +341,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -373,12 +373,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -390,54 +389,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="21">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="28" formatCode="mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -470,10 +433,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -485,10 +445,10 @@
       <numFmt numFmtId="28" formatCode="mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -520,7 +480,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Saffron Table – Customer Experience &amp; Rewards Survey(1-25).xlsx]Sheet2!PivotTable7</c:name>
+    <c:name>[Ex5B_FinalResults.xlsx]Sheet2!PivotTable7</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -574,8 +534,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -636,6 +595,60 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -684,6 +697,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-9F52-1646-B101-59AEC180B340}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -703,6 +721,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-9F52-1646-B101-59AEC180B340}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -722,6 +745,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-9F52-1646-B101-59AEC180B340}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1020,7 +1048,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Saffron Table – Customer Experience &amp; Rewards Survey(1-25).xlsx]Sheet2!PivotTable11</c:name>
+    <c:name>[Ex5B_FinalResults.xlsx]Sheet2!PivotTable11</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1074,8 +1102,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1136,6 +1163,186 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1174,6 +1381,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1193,6 +1405,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1212,6 +1429,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1231,6 +1453,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1250,6 +1477,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1269,6 +1501,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1290,6 +1527,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1311,6 +1553,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1332,6 +1579,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1353,6 +1605,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1374,6 +1631,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-EC58-C642-9A60-2FFC8AEF7EFF}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3060,10 +3322,10 @@
     <cacheField name="ID" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="25"/>
     </cacheField>
-    <cacheField name="Start time" numFmtId="166">
+    <cacheField name="Start time" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-07T19:13:44" maxDate="2026-04-09T14:11:28"/>
     </cacheField>
-    <cacheField name="Completion time" numFmtId="166">
+    <cacheField name="Completion time" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-07T19:14:39" maxDate="2026-04-09T14:11:39"/>
     </cacheField>
     <cacheField name="Time to Complete" numFmtId="45">
@@ -3075,7 +3337,7 @@
     <cacheField name="Name" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="Last modified time" numFmtId="165">
+    <cacheField name="Last modified time" numFmtId="164">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="What is your age?" numFmtId="0">
@@ -3614,12 +3876,123 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A984F13E-E72F-5242-92DD-FA713CF75B8A}" name="PivotTable11" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B873DE2C-D5ED-7949-B504-5294481F555C}" name="PivotTable7" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="17">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="45" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Name" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A984F13E-E72F-5242-92DD-FA713CF75B8A}" name="PivotTable11" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A21:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="45" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -3713,7 +4086,7 @@
   <dataFields count="1">
     <dataField name="Sum of How likely are you to return to our restaurant?" fld="14" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="11">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -3723,77 +4096,152 @@
         </references>
       </pivotArea>
     </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B873DE2C-D5ED-7949-B504-5294481F555C}" name="PivotTable7" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="17">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="45" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Name" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="0" format="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
+        <references count="3">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -3815,28 +4263,27 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:Q27" totalsRowCount="1">
   <autoFilter ref="A1:Q26" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="33" totalsRowDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="32" totalsRowDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="31" totalsRowDxfId="14"/>
-    <tableColumn id="17" xr3:uid="{07F1E1E5-4E03-5E45-B624-5B37C22604C9}" name="Time to Complete" totalsRowFunction="custom" dataDxfId="30" totalsRowDxfId="13">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="19" totalsRowDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="18" totalsRowDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{07F1E1E5-4E03-5E45-B624-5B37C22604C9}" name="Time to Complete" dataDxfId="17" totalsRowDxfId="1">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
-      <totalsRowFormula>AVERAGE(Table1[Time to Complete])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="29" totalsRowDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="28" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Last modified time" dataDxfId="27" totalsRowDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="What is your age?" dataDxfId="26" totalsRowDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="What is your gender?" dataDxfId="25" totalsRowDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Where are you visiting from?" dataDxfId="24" totalsRowDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="How often do you visit our restaurant?" dataDxfId="23" totalsRowDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Food" dataDxfId="22" totalsRowDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Service" dataDxfId="21" totalsRowDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Atmosphere" dataDxfId="20" totalsRowDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="How likely are you to return to our restaurant?" totalsRowFunction="custom" dataDxfId="19" totalsRowDxfId="2">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Last modified time" dataDxfId="14" totalsRowDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="What is your age?" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="What is your gender?" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Where are you visiting from?" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="How often do you visit our restaurant?" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Food" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Service" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Atmosphere" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="How likely are you to return to our restaurant?" totalsRowFunction="custom" dataDxfId="6">
       <totalsRowFormula>AVERAGE(Table1[How likely are you to return to our restaurant?])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Would you be interested in a rewards program or special promotions?" dataDxfId="18" totalsRowDxfId="1"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Is there anything we could improve? (optional)" dataDxfId="17" totalsRowDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Would you be interested in a rewards program or special promotions?" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Is there anything we could improve? (optional)" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4147,7 +4594,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B1" t="s">
@@ -4155,39 +4602,39 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B21" t="s">
@@ -4195,126 +4642,124 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24">
         <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26">
         <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27">
         <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28">
         <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29">
         <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30">
         <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32">
         <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33">
         <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34">
         <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="4"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="4"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37">
         <v>199</v>
       </c>
     </row>
@@ -4334,8 +4779,12 @@
     <col min="4" max="4" width="20" style="3" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="27.33203125" customWidth="1"/>
-    <col min="7" max="15" width="20" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="30.33203125" customWidth="1"/>
+    <col min="7" max="9" width="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5" customWidth="1"/>
+    <col min="11" max="11" width="36.33203125" customWidth="1"/>
+    <col min="12" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="38.33203125" customWidth="1"/>
+    <col min="16" max="16" width="56.83203125" customWidth="1"/>
     <col min="17" max="17" width="42.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5621,27 +6070,11 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-      <c r="D27" s="3">
-        <f>AVERAGE(Table1[Time to Complete])</f>
-        <v>3.4196296296722724E-2</v>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4">
+      <c r="O27">
         <f>AVERAGE(Table1[How likely are you to return to our restaurant?])</f>
         <v>8.2916666666666661</v>
       </c>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
